--- a/data/trans_bre/Q45B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,64</t>
+          <t>0,73; 2,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,89</t>
+          <t>-0,46; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,33</t>
+          <t>-1,43; 0,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,86; 845,56</t>
+          <t>34,27; 762,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 159,46</t>
+          <t>-20,92; 175,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,2; 90,47</t>
+          <t>-85,36; 105,43</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,29</t>
+          <t>6,76; 10,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,9</t>
+          <t>4,74; 7,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,54</t>
+          <t>2,66; 4,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242,85; 587,04</t>
+          <t>240,09; 574,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>150,01; 366,77</t>
+          <t>146,58; 370,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>210,58; 831,57</t>
+          <t>244,91; 860,27</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,2</t>
+          <t>6,29; 13,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 16,55</t>
+          <t>8,2; 16,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,71</t>
+          <t>2,41; 6,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115,55; 526,38</t>
+          <t>105,45; 550,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>150,16; 729,63</t>
+          <t>154,66; 761,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>101,39; 921,64</t>
+          <t>93,78; 893,11</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,87</t>
+          <t>4,74; 6,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,04</t>
+          <t>3,86; 6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,2</t>
+          <t>1,88; 3,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196,86; 418,43</t>
+          <t>195,49; 412,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>132,2; 278,19</t>
+          <t>130,03; 281,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>144,77; 447,58</t>
+          <t>157,2; 466,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Q45B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,65</t>
+          <t>0,83; 2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,02</t>
+          <t>-0,39; 1,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,4</t>
+          <t>-1,3; 0,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,27; 762,9</t>
+          <t>66,55; 953,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 175,52</t>
+          <t>-18,15; 165,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,36; 105,43</t>
+          <t>-83,72; 92,26</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,13</t>
+          <t>6,63; 10,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,89</t>
+          <t>4,88; 7,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,6</t>
+          <t>2,51; 4,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>240,09; 574,1</t>
+          <t>226,35; 579,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>146,58; 370,84</t>
+          <t>149,94; 384,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>244,91; 860,27</t>
+          <t>231,25; 888,64</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 13,3</t>
+          <t>5,97; 13,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 16,21</t>
+          <t>8,72; 16,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,75</t>
+          <t>2,51; 6,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105,45; 550,75</t>
+          <t>105,73; 540,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>154,66; 761,78</t>
+          <t>148,96; 679,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,78; 893,11</t>
+          <t>112,04; 916,67</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,87</t>
+          <t>4,85; 6,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,0</t>
+          <t>3,9; 6,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,27</t>
+          <t>1,86; 3,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195,49; 412,09</t>
+          <t>198,07; 411,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>130,03; 281,2</t>
+          <t>132,64; 292,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>157,2; 466,86</t>
+          <t>151,88; 455,63</t>
         </is>
       </c>
     </row>
